--- a/fixtures/files/workbuster_deltagare_MBAB.xlsx
+++ b/fixtures/files/workbuster_deltagare_MBAB.xlsx
@@ -467,7 +467,7 @@
         <v>Mohammed Johansson</v>
       </c>
       <c r="C5" t="str">
-        <v>950315-9288</v>
+        <v>950315-9981</v>
       </c>
       <c r="D5" t="str">
         <v>ROM2</v>
@@ -487,7 +487,7 @@
         <v>Noor Hansson</v>
       </c>
       <c r="C6" t="str">
-        <v>690715-9369</v>
+        <v>690715-9989</v>
       </c>
       <c r="D6" t="str">
         <v>Karriärvägledning</v>
@@ -516,7 +516,7 @@
         <v>Elin Axelsson</v>
       </c>
       <c r="C7" t="str">
-        <v>040229-9564</v>
+        <v>040229-9994</v>
       </c>
       <c r="D7" t="str">
         <v>Karriärvägledning</v>
@@ -539,7 +539,7 @@
         <v>Filip Hassan</v>
       </c>
       <c r="C8" t="str">
-        <v>960119-2595</v>
+        <v>960119-9855</v>
       </c>
       <c r="D8" t="str">
         <v>Karriärvägledning</v>
@@ -562,7 +562,7 @@
         <v>Selma Bengtsson</v>
       </c>
       <c r="C9" t="str">
-        <v>930924-3823</v>
+        <v>930924-9879</v>
       </c>
       <c r="D9" t="str">
         <v>ROM2</v>
@@ -591,7 +591,7 @@
         <v>Ida Nyström</v>
       </c>
       <c r="C10" t="str">
-        <v>820125-3476</v>
+        <v>820125-9861</v>
       </c>
       <c r="D10" t="str">
         <v>KROM</v>
@@ -614,7 +614,7 @@
         <v>Anna Larsson</v>
       </c>
       <c r="C11" t="str">
-        <v>650627-0823</v>
+        <v>650627-9816</v>
       </c>
       <c r="D11" t="str">
         <v>ROM2</v>
@@ -634,7 +634,7 @@
         <v>Sara Jakobsson</v>
       </c>
       <c r="C12" t="str">
-        <v>690102-5277</v>
+        <v>690102-9907</v>
       </c>
       <c r="D12" t="str">
         <v>ROM2</v>
@@ -654,7 +654,7 @@
         <v>Agnes Jansson</v>
       </c>
       <c r="C13" t="str">
-        <v>001103-4741</v>
+        <v>001103-9898</v>
       </c>
       <c r="D13" t="str">
         <v>ROM2</v>
@@ -677,7 +677,7 @@
         <v>Anna Kaya</v>
       </c>
       <c r="C14" t="str">
-        <v>731002-4042</v>
+        <v>731002-9884</v>
       </c>
       <c r="D14" t="str">
         <v>Karriärvägledning</v>
@@ -700,7 +700,7 @@
         <v>Vera Wallin</v>
       </c>
       <c r="C15" t="str">
-        <v>760126-4703</v>
+        <v>760126-9892</v>
       </c>
       <c r="D15" t="str">
         <v>ROM2</v>
@@ -723,7 +723,7 @@
         <v>Nadia Jansson</v>
       </c>
       <c r="C16" t="str">
-        <v>930410-5894</v>
+        <v>930410-9912</v>
       </c>
       <c r="D16" t="str">
         <v>KVL</v>
@@ -752,7 +752,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="C17" t="str">
-        <v>960324-6803</v>
+        <v>960324-9930</v>
       </c>
       <c r="D17" t="str">
         <v>Karriärvägledning</v>
@@ -781,7 +781,7 @@
         <v>Abdi Nordin</v>
       </c>
       <c r="C18" t="str">
-        <v>941123-0411</v>
+        <v>941123-9800</v>
       </c>
       <c r="D18" t="str">
         <v>ROM2</v>
@@ -801,7 +801,7 @@
         <v>Adam Kaya</v>
       </c>
       <c r="C19" t="str">
-        <v>681211-4806</v>
+        <v>681211-9896</v>
       </c>
       <c r="D19" t="str">
         <v>ROM2</v>
@@ -830,7 +830,7 @@
         <v>Ali Ström</v>
       </c>
       <c r="C20" t="str">
-        <v>001213-0423</v>
+        <v>001213-9804</v>
       </c>
       <c r="D20" t="str">
         <v>Karriärvägledning</v>
@@ -859,7 +859,7 @@
         <v>Elias Mohamed</v>
       </c>
       <c r="C21" t="str">
-        <v>900710-9888</v>
+        <v>900710-9995</v>
       </c>
       <c r="D21" t="str">
         <v>ROM2</v>
@@ -879,7 +879,7 @@
         <v>Linnea Berg</v>
       </c>
       <c r="C22" t="str">
-        <v>940820-0039</v>
+        <v>940820-9808</v>
       </c>
       <c r="D22" t="str">
         <v>ROM2</v>
@@ -899,7 +899,7 @@
         <v>Jonas Mattsson</v>
       </c>
       <c r="C23" t="str">
-        <v>730603-3171</v>
+        <v>730603-9863</v>
       </c>
       <c r="D23" t="str">
         <v>ROM2</v>
@@ -919,7 +919,7 @@
         <v>Hassan Demir</v>
       </c>
       <c r="C24" t="str">
-        <v>031013-9571</v>
+        <v>031013-9993</v>
       </c>
       <c r="D24" t="str">
         <v>ROM2</v>
@@ -942,7 +942,7 @@
         <v>Isak Lundin</v>
       </c>
       <c r="C25" t="str">
-        <v>750320-6844</v>
+        <v>750320-9939</v>
       </c>
       <c r="D25" t="str">
         <v>KROM</v>
@@ -962,7 +962,7 @@
         <v>Nadia Lindqvist</v>
       </c>
       <c r="C26" t="str">
-        <v>750609-5954</v>
+        <v>750609-9915</v>
       </c>
       <c r="D26" t="str">
         <v>ROM2</v>
@@ -985,7 +985,7 @@
         <v>Yasmin Demir</v>
       </c>
       <c r="C27" t="str">
-        <v>720817-0584</v>
+        <v>720817-9817</v>
       </c>
       <c r="D27" t="str">
         <v>ROM2</v>
@@ -1005,7 +1005,7 @@
         <v>Hugo Ström</v>
       </c>
       <c r="C28" t="str">
-        <v>670228-0980</v>
+        <v>670228-9817</v>
       </c>
       <c r="D28" t="str">
         <v>KROM</v>
@@ -1025,7 +1025,7 @@
         <v>Wilma Mohamed</v>
       </c>
       <c r="C29" t="str">
-        <v>870420-1634</v>
+        <v>870420-9835</v>
       </c>
       <c r="D29" t="str">
         <v>ROM2</v>
@@ -1045,7 +1045,7 @@
         <v>Erik Axelsson</v>
       </c>
       <c r="C30" t="str">
-        <v>860706-3438</v>
+        <v>860706-9864</v>
       </c>
       <c r="D30" t="str">
         <v>KROM</v>
@@ -1074,7 +1074,7 @@
         <v>Johan Wallin</v>
       </c>
       <c r="C31" t="str">
-        <v>740210-9628</v>
+        <v>740210-9990</v>
       </c>
       <c r="D31" t="str">
         <v>ROM2</v>
@@ -1097,7 +1097,7 @@
         <v>Anna Lindström</v>
       </c>
       <c r="C32" t="str">
-        <v>031015-3374</v>
+        <v>031015-9868</v>
       </c>
       <c r="D32" t="str">
         <v>KVL</v>
@@ -1126,7 +1126,7 @@
         <v>Fatima Bergström</v>
       </c>
       <c r="C33" t="str">
-        <v>941121-6758</v>
+        <v>941121-9935</v>
       </c>
       <c r="D33" t="str">
         <v>KROM</v>
@@ -1155,7 +1155,7 @@
         <v>Jonas Engström</v>
       </c>
       <c r="C34" t="str">
-        <v>930604-0735</v>
+        <v>930604-9819</v>
       </c>
       <c r="D34" t="str">
         <v>ROM2</v>
@@ -1184,7 +1184,7 @@
         <v>Gustav Åberg</v>
       </c>
       <c r="C35" t="str">
-        <v>940706-8502</v>
+        <v>940706-9963</v>
       </c>
       <c r="D35" t="str">
         <v>KROM</v>
@@ -1207,7 +1207,7 @@
         <v>Anna Holm</v>
       </c>
       <c r="C36" t="str">
-        <v>740901-5331</v>
+        <v>740901-9903</v>
       </c>
       <c r="D36" t="str">
         <v>KVL</v>
@@ -1227,7 +1227,7 @@
         <v>Noor Olsson</v>
       </c>
       <c r="C37" t="str">
-        <v>670706-1708</v>
+        <v>670706-9834</v>
       </c>
       <c r="D37" t="str">
         <v>KROM</v>
@@ -1256,7 +1256,7 @@
         <v>Wilma Svensson</v>
       </c>
       <c r="C38" t="str">
-        <v>870109-6003</v>
+        <v>870109-9924</v>
       </c>
       <c r="D38" t="str">
         <v>KROM</v>
@@ -1279,7 +1279,7 @@
         <v>Klara Svensson</v>
       </c>
       <c r="C39" t="str">
-        <v>820529-3593</v>
+        <v>820529-9871</v>
       </c>
       <c r="D39" t="str">
         <v>ROM2</v>
@@ -1299,7 +1299,7 @@
         <v>Ibrahim Gustafsson</v>
       </c>
       <c r="C40" t="str">
-        <v>680227-5948</v>
+        <v>680227-9916</v>
       </c>
       <c r="D40" t="str">
         <v>KROM</v>
@@ -1322,7 +1322,7 @@
         <v>Karl Lindqvist</v>
       </c>
       <c r="C41" t="str">
-        <v>930123-2162</v>
+        <v>930123-9845</v>
       </c>
       <c r="D41" t="str">
         <v>KROM</v>
@@ -1342,7 +1342,7 @@
         <v>Klara Lundin</v>
       </c>
       <c r="C42" t="str">
-        <v>790805-0722</v>
+        <v>790805-9814</v>
       </c>
       <c r="D42" t="str">
         <v>Karriärvägledning</v>
@@ -1365,7 +1365,7 @@
         <v>Mohammed Larsson</v>
       </c>
       <c r="C43" t="str">
-        <v>780602-1544</v>
+        <v>780602-9836</v>
       </c>
       <c r="D43" t="str">
         <v>Karriärvägledning</v>
@@ -1388,7 +1388,7 @@
         <v>Agnes Magnusson</v>
       </c>
       <c r="C44" t="str">
-        <v>680402-8774</v>
+        <v>680402-9970</v>
       </c>
       <c r="D44" t="str">
         <v>KROM</v>
@@ -1408,7 +1408,7 @@
         <v>Ali Andersson</v>
       </c>
       <c r="C45" t="str">
-        <v>000428-7926</v>
+        <v>000428-9955</v>
       </c>
       <c r="D45" t="str">
         <v>KROM</v>
@@ -1431,7 +1431,7 @@
         <v>Sara Gustafsson</v>
       </c>
       <c r="C46" t="str">
-        <v>010117-4712</v>
+        <v>010117-9893</v>
       </c>
       <c r="D46" t="str">
         <v>KROM</v>
@@ -1451,7 +1451,7 @@
         <v>Fatima Ahmed</v>
       </c>
       <c r="C47" t="str">
-        <v>970822-6411</v>
+        <v>970822-9928</v>
       </c>
       <c r="D47" t="str">
         <v>Karriärvägledning</v>
@@ -1474,7 +1474,7 @@
         <v>Dalia Lindqvist</v>
       </c>
       <c r="C48" t="str">
-        <v>980323-6257</v>
+        <v>980323-9921</v>
       </c>
       <c r="D48" t="str">
         <v>Karriärvägledning</v>
@@ -1494,7 +1494,7 @@
         <v>Anna Eklund</v>
       </c>
       <c r="C49" t="str">
-        <v>951111-0604</v>
+        <v>951111-9811</v>
       </c>
       <c r="D49" t="str">
         <v>Karriärvägledning</v>
@@ -1523,7 +1523,7 @@
         <v>Hugo Sandberg</v>
       </c>
       <c r="C50" t="str">
-        <v>660419-9445</v>
+        <v>660419-9981</v>
       </c>
       <c r="D50" t="str">
         <v>KROM</v>
@@ -1543,7 +1543,7 @@
         <v>Rania Karlsson</v>
       </c>
       <c r="C51" t="str">
-        <v>920825-0408</v>
+        <v>920825-9805</v>
       </c>
       <c r="D51" t="str">
         <v>ROM2</v>
@@ -1563,7 +1563,7 @@
         <v>Lina Eklund</v>
       </c>
       <c r="C52" t="str">
-        <v>881129-6766</v>
+        <v>881129-9935</v>
       </c>
       <c r="D52" t="str">
         <v>ROM2</v>
@@ -1592,7 +1592,7 @@
         <v>Leila Öberg</v>
       </c>
       <c r="C53" t="str">
-        <v>991217-4878</v>
+        <v>991217-9893</v>
       </c>
       <c r="D53" t="str">
         <v>ROM2</v>
@@ -1621,7 +1621,7 @@
         <v>Jonas Johansson</v>
       </c>
       <c r="C54" t="str">
-        <v>970325-1398</v>
+        <v>970325-9821</v>
       </c>
       <c r="D54" t="str">
         <v>ROM2</v>
@@ -1644,7 +1644,7 @@
         <v>Erik Danielsson</v>
       </c>
       <c r="C55" t="str">
-        <v>680919-3250</v>
+        <v>680919-9869</v>
       </c>
       <c r="D55" t="str">
         <v>ROM2</v>
@@ -1667,7 +1667,7 @@
         <v>Axel Svensson</v>
       </c>
       <c r="C56" t="str">
-        <v>771126-0930</v>
+        <v>771126-9816</v>
       </c>
       <c r="D56" t="str">
         <v>ROM2</v>
@@ -1690,7 +1690,7 @@
         <v>Elias Jakobsson</v>
       </c>
       <c r="C57" t="str">
-        <v>621217-1315</v>
+        <v>621217-9821</v>
       </c>
       <c r="D57" t="str">
         <v>ROM2</v>
@@ -1713,7 +1713,7 @@
         <v>Isak Sandberg</v>
       </c>
       <c r="C58" t="str">
-        <v>020128-0518</v>
+        <v>020128-9816</v>
       </c>
       <c r="D58" t="str">
         <v>Karriärvägledning</v>
@@ -1736,7 +1736,7 @@
         <v>Lucas Ahmed</v>
       </c>
       <c r="C59" t="str">
-        <v>870908-2054</v>
+        <v>870908-9844</v>
       </c>
       <c r="D59" t="str">
         <v>ROM2</v>
@@ -1765,7 +1765,7 @@
         <v>Gustav Karlsson</v>
       </c>
       <c r="C60" t="str">
-        <v>881109-0797</v>
+        <v>881109-9814</v>
       </c>
       <c r="D60" t="str">
         <v>KROM</v>
@@ -1788,7 +1788,7 @@
         <v>Aisha Hansson</v>
       </c>
       <c r="C61" t="str">
-        <v>990521-8070</v>
+        <v>990521-9961</v>
       </c>
       <c r="D61" t="str">
         <v>ROM2</v>
@@ -1817,7 +1817,7 @@
         <v>Lina Jansson</v>
       </c>
       <c r="C62" t="str">
-        <v>860518-5977</v>
+        <v>860518-9912</v>
       </c>
       <c r="D62" t="str">
         <v>KVL</v>
@@ -1840,7 +1840,7 @@
         <v>Linnea Ali</v>
       </c>
       <c r="C63" t="str">
-        <v>680216-0629</v>
+        <v>680216-9810</v>
       </c>
       <c r="D63" t="str">
         <v>ROM2</v>
@@ -1869,7 +1869,7 @@
         <v>Aisha Fransson</v>
       </c>
       <c r="C64" t="str">
-        <v>861211-4218</v>
+        <v>861211-9886</v>
       </c>
       <c r="D64" t="str">
         <v>ROM2</v>
@@ -1892,7 +1892,7 @@
         <v>Hiba Johansson</v>
       </c>
       <c r="C65" t="str">
-        <v>800813-1727</v>
+        <v>800813-9837</v>
       </c>
       <c r="D65" t="str">
         <v>KROM</v>
@@ -1915,7 +1915,7 @@
         <v>Aisha Åberg</v>
       </c>
       <c r="C66" t="str">
-        <v>870825-1445</v>
+        <v>870825-9828</v>
       </c>
       <c r="D66" t="str">
         <v>ROM2</v>
@@ -1935,7 +1935,7 @@
         <v>Elin Jakobsson</v>
       </c>
       <c r="C67" t="str">
-        <v>650129-9322</v>
+        <v>650129-9983</v>
       </c>
       <c r="D67" t="str">
         <v>ROM2</v>
@@ -1964,7 +1964,7 @@
         <v>Maja Jonsson</v>
       </c>
       <c r="C68" t="str">
-        <v>960917-3894</v>
+        <v>960917-9875</v>
       </c>
       <c r="D68" t="str">
         <v>KVL</v>
@@ -1987,7 +1987,7 @@
         <v>Ibrahim Nilsson</v>
       </c>
       <c r="C69" t="str">
-        <v>680805-1392</v>
+        <v>680805-9825</v>
       </c>
       <c r="D69" t="str">
         <v>KROM</v>
@@ -2010,7 +2010,7 @@
         <v>Ali Åberg</v>
       </c>
       <c r="C70" t="str">
-        <v>030719-9620</v>
+        <v>030719-9992</v>
       </c>
       <c r="D70" t="str">
         <v>KROM</v>
@@ -2033,7 +2033,7 @@
         <v>Johan Hussein</v>
       </c>
       <c r="C71" t="str">
-        <v>680301-4536</v>
+        <v>680301-9899</v>
       </c>
       <c r="D71" t="str">
         <v>KROM</v>
@@ -2062,7 +2062,7 @@
         <v>Maja Danielsson</v>
       </c>
       <c r="C72" t="str">
-        <v>711130-2621</v>
+        <v>711130-9857</v>
       </c>
       <c r="D72" t="str">
         <v>KROM</v>
@@ -2085,7 +2085,7 @@
         <v>Elias Öberg</v>
       </c>
       <c r="C73" t="str">
-        <v>850708-6018</v>
+        <v>850708-9921</v>
       </c>
       <c r="D73" t="str">
         <v>KROM</v>
@@ -2105,7 +2105,7 @@
         <v>Amina Holm</v>
       </c>
       <c r="C74" t="str">
-        <v>980417-5645</v>
+        <v>980417-9910</v>
       </c>
       <c r="D74" t="str">
         <v>KROM</v>
@@ -2134,7 +2134,7 @@
         <v>Samir Jonsson</v>
       </c>
       <c r="C75" t="str">
-        <v>770619-5174</v>
+        <v>770619-9903</v>
       </c>
       <c r="D75" t="str">
         <v>ROM2</v>
@@ -2163,7 +2163,7 @@
         <v>Zainab Demir</v>
       </c>
       <c r="C76" t="str">
-        <v>850420-8987</v>
+        <v>850420-9977</v>
       </c>
       <c r="D76" t="str">
         <v>ROM2</v>
@@ -2192,7 +2192,7 @@
         <v>Hassan Kaya</v>
       </c>
       <c r="C77" t="str">
-        <v>770328-1860</v>
+        <v>770328-9830</v>
       </c>
       <c r="D77" t="str">
         <v>ROM2</v>
@@ -2212,7 +2212,7 @@
         <v>Fatima Karlsson</v>
       </c>
       <c r="C78" t="str">
-        <v>710401-4928</v>
+        <v>710401-9893</v>
       </c>
       <c r="D78" t="str">
         <v>KROM</v>
@@ -2235,7 +2235,7 @@
         <v>Emil Nilsson</v>
       </c>
       <c r="C79" t="str">
-        <v>040615-7099</v>
+        <v>040615-9947</v>
       </c>
       <c r="D79" t="str">
         <v>ROM2</v>
@@ -2264,7 +2264,7 @@
         <v>Lucas Pettersson</v>
       </c>
       <c r="C80" t="str">
-        <v>911106-3732</v>
+        <v>911106-9879</v>
       </c>
       <c r="D80" t="str">
         <v>ROM2</v>
@@ -2293,7 +2293,7 @@
         <v>Lucas Holm</v>
       </c>
       <c r="C81" t="str">
-        <v>781224-8743</v>
+        <v>781224-9972</v>
       </c>
       <c r="D81" t="str">
         <v>ROM2</v>
@@ -2313,7 +2313,7 @@
         <v>Isak Eriksson</v>
       </c>
       <c r="C82" t="str">
-        <v>800723-8291</v>
+        <v>800723-9968</v>
       </c>
       <c r="D82" t="str">
         <v>KROM</v>
@@ -2336,7 +2336,7 @@
         <v>Nadia Mohamed</v>
       </c>
       <c r="C83" t="str">
-        <v>660120-9312</v>
+        <v>660120-9981</v>
       </c>
       <c r="D83" t="str">
         <v>Karriärvägledning</v>
@@ -2365,7 +2365,7 @@
         <v>Adam Nordin</v>
       </c>
       <c r="C84" t="str">
-        <v>751203-3361</v>
+        <v>751203-9863</v>
       </c>
       <c r="D84" t="str">
         <v>KROM</v>
@@ -2394,7 +2394,7 @@
         <v>Mohammed Ali</v>
       </c>
       <c r="C85" t="str">
-        <v>690618-2586</v>
+        <v>690618-9854</v>
       </c>
       <c r="D85" t="str">
         <v>Karriärvägledning</v>
@@ -2414,7 +2414,7 @@
         <v>Elias Persson</v>
       </c>
       <c r="C86" t="str">
-        <v>970604-4568</v>
+        <v>970604-9898</v>
       </c>
       <c r="D86" t="str">
         <v>ROM2</v>
@@ -2443,7 +2443,7 @@
         <v>Hiba Pettersson</v>
       </c>
       <c r="C87" t="str">
-        <v>001105-8666</v>
+        <v>001105-9979</v>
       </c>
       <c r="D87" t="str">
         <v>ROM2</v>
@@ -2466,7 +2466,7 @@
         <v>Lucas Åberg</v>
       </c>
       <c r="C88" t="str">
-        <v>970920-0621</v>
+        <v>970920-9812</v>
       </c>
       <c r="D88" t="str">
         <v>ROM2</v>
@@ -2492,7 +2492,7 @@
         <v>Elias Nordin</v>
       </c>
       <c r="C89" t="str">
-        <v>700825-5817</v>
+        <v>700825-9918</v>
       </c>
       <c r="D89" t="str">
         <v>ROM2</v>
@@ -2515,7 +2515,7 @@
         <v>Elias Åberg</v>
       </c>
       <c r="C90" t="str">
-        <v>631014-8215</v>
+        <v>631014-9965</v>
       </c>
       <c r="D90" t="str">
         <v>ROM2</v>
@@ -2538,7 +2538,7 @@
         <v>Arvid Jansson</v>
       </c>
       <c r="C91" t="str">
-        <v>020102-2787</v>
+        <v>020102-9857</v>
       </c>
       <c r="D91" t="str">
         <v>ROM2</v>
@@ -2561,7 +2561,7 @@
         <v>Ibrahim Öberg</v>
       </c>
       <c r="C92" t="str">
-        <v>740623-3754</v>
+        <v>740623-9876</v>
       </c>
       <c r="D92" t="str">
         <v>KVL</v>
@@ -2584,7 +2584,7 @@
         <v>Lina Pettersson</v>
       </c>
       <c r="C93" t="str">
-        <v>940823-3345</v>
+        <v>940823-9862</v>
       </c>
       <c r="D93" t="str">
         <v>KROM</v>
@@ -2604,7 +2604,7 @@
         <v>Omar Nilsson</v>
       </c>
       <c r="C94" t="str">
-        <v>821124-7088</v>
+        <v>821124-9944</v>
       </c>
       <c r="D94" t="str">
         <v>ROM2</v>
@@ -2627,7 +2627,7 @@
         <v>Tilda Nordin</v>
       </c>
       <c r="C95" t="str">
-        <v>840620-0454</v>
+        <v>840620-9802</v>
       </c>
       <c r="D95" t="str">
         <v>KVL</v>
@@ -2656,7 +2656,7 @@
         <v>Hanna Lundin</v>
       </c>
       <c r="C96" t="str">
-        <v>670717-5995</v>
+        <v>670717-9914</v>
       </c>
       <c r="D96" t="str">
         <v>KROM</v>
@@ -2685,7 +2685,7 @@
         <v>Adam Axelsson</v>
       </c>
       <c r="C97" t="str">
-        <v>880311-7087</v>
+        <v>880311-9943</v>
       </c>
       <c r="D97" t="str">
         <v>KROM</v>
@@ -2708,7 +2708,7 @@
         <v>Viktor Nordin</v>
       </c>
       <c r="C98" t="str">
-        <v>880824-5438</v>
+        <v>880824-9901</v>
       </c>
       <c r="D98" t="str">
         <v>KVL</v>
@@ -2731,7 +2731,7 @@
         <v>Fatima Johansson</v>
       </c>
       <c r="C99" t="str">
-        <v>640326-9019</v>
+        <v>640326-9985</v>
       </c>
       <c r="D99" t="str">
         <v>ROM2</v>
@@ -2760,7 +2760,7 @@
         <v>Adam Andersson</v>
       </c>
       <c r="C100" t="str">
-        <v>911018-9298</v>
+        <v>911018-9983</v>
       </c>
       <c r="D100" t="str">
         <v>ROM2</v>
@@ -2783,7 +2783,7 @@
         <v>Ibrahim Olsson</v>
       </c>
       <c r="C101" t="str">
-        <v>810412-6324</v>
+        <v>810412-9922</v>
       </c>
       <c r="D101" t="str">
         <v>KROM</v>
@@ -2812,7 +2812,7 @@
         <v>Nadia Persson</v>
       </c>
       <c r="C102" t="str">
-        <v>711223-9947</v>
+        <v>711223-9996</v>
       </c>
       <c r="D102" t="str">
         <v>ROM2</v>
@@ -2835,7 +2835,7 @@
         <v>Kerim Nilsson</v>
       </c>
       <c r="C103" t="str">
-        <v>800306-9351</v>
+        <v>800306-9989</v>
       </c>
       <c r="D103" t="str">
         <v>ROM2</v>
@@ -2858,7 +2858,7 @@
         <v>Omar Pettersson</v>
       </c>
       <c r="C104" t="str">
-        <v>810227-5065</v>
+        <v>810227-9901</v>
       </c>
       <c r="D104" t="str">
         <v>KROM</v>
@@ -2887,7 +2887,7 @@
         <v>Ida Fransson</v>
       </c>
       <c r="C105" t="str">
-        <v>820121-7877</v>
+        <v>820121-9956</v>
       </c>
       <c r="D105" t="str">
         <v>KROM</v>
@@ -2910,7 +2910,7 @@
         <v>Saga Sjöberg</v>
       </c>
       <c r="C106" t="str">
-        <v>921213-5942</v>
+        <v>921213-9910</v>
       </c>
       <c r="D106" t="str">
         <v>ROM2</v>
@@ -2939,7 +2939,7 @@
         <v>Filip Forsberg</v>
       </c>
       <c r="C107" t="str">
-        <v>000522-3219</v>
+        <v>000522-9869</v>
       </c>
       <c r="D107" t="str">
         <v>ROM2</v>
@@ -2962,7 +2962,7 @@
         <v>Amina Axelsson</v>
       </c>
       <c r="C108" t="str">
-        <v>781104-1057</v>
+        <v>781104-9829</v>
       </c>
       <c r="D108" t="str">
         <v>ROM2</v>
@@ -2985,7 +2985,7 @@
         <v>Klara Danielsson</v>
       </c>
       <c r="C109" t="str">
-        <v>621112-2087</v>
+        <v>621112-9843</v>
       </c>
       <c r="D109" t="str">
         <v>ROM2</v>
@@ -3014,7 +3014,7 @@
         <v>Karl Yilmaz</v>
       </c>
       <c r="C110" t="str">
-        <v>760118-5668</v>
+        <v>760118-9918</v>
       </c>
       <c r="D110" t="str">
         <v>Karriärvägledning</v>
@@ -3043,7 +3043,7 @@
         <v>Erik Ström</v>
       </c>
       <c r="C111" t="str">
-        <v>941209-0608</v>
+        <v>941209-9815</v>
       </c>
       <c r="D111" t="str">
         <v>ROM2</v>
@@ -3063,7 +3063,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="C112" t="str">
-        <v>040201-9525</v>
+        <v>040201-9996</v>
       </c>
       <c r="D112" t="str">
         <v>KROM</v>
@@ -3092,7 +3092,7 @@
         <v>Elin Fransson</v>
       </c>
       <c r="C113" t="str">
-        <v>750512-5265</v>
+        <v>750512-9903</v>
       </c>
       <c r="D113" t="str">
         <v>ROM2</v>
@@ -3121,7 +3121,7 @@
         <v>Rania Lundin</v>
       </c>
       <c r="C114" t="str">
-        <v>970926-4247</v>
+        <v>970926-9881</v>
       </c>
       <c r="D114" t="str">
         <v>Karriärvägledning</v>
@@ -3144,7 +3144,7 @@
         <v>Hiba Svensson</v>
       </c>
       <c r="C115" t="str">
-        <v>961010-2759</v>
+        <v>961010-9853</v>
       </c>
       <c r="D115" t="str">
         <v>KROM</v>
@@ -3164,7 +3164,7 @@
         <v>Mariam Fransson</v>
       </c>
       <c r="C116" t="str">
-        <v>000913-2044</v>
+        <v>000913-9841</v>
       </c>
       <c r="D116" t="str">
         <v>KROM</v>
@@ -3187,7 +3187,7 @@
         <v>Jakob Nilsson</v>
       </c>
       <c r="C117" t="str">
-        <v>990302-8943</v>
+        <v>990302-9974</v>
       </c>
       <c r="D117" t="str">
         <v>Karriärvägledning</v>
@@ -3210,7 +3210,7 @@
         <v>Sofia Mohamed</v>
       </c>
       <c r="C118" t="str">
-        <v>750331-9845</v>
+        <v>750331-9993</v>
       </c>
       <c r="D118" t="str">
         <v>KROM</v>
@@ -3239,7 +3239,7 @@
         <v>Hiba Hansson</v>
       </c>
       <c r="C119" t="str">
-        <v>730213-4593</v>
+        <v>730213-9899</v>
       </c>
       <c r="D119" t="str">
         <v>KROM</v>
@@ -3259,7 +3259,7 @@
         <v>Hugo Magnusson</v>
       </c>
       <c r="C120" t="str">
-        <v>030528-4150</v>
+        <v>030528-9886</v>
       </c>
       <c r="D120" t="str">
         <v>ROM2</v>
@@ -3282,7 +3282,7 @@
         <v>Linnea Söderberg</v>
       </c>
       <c r="C121" t="str">
-        <v>910831-5673</v>
+        <v>910831-9915</v>
       </c>
       <c r="D121" t="str">
         <v>KROM</v>
@@ -3311,7 +3311,7 @@
         <v>Hiba Jonsson</v>
       </c>
       <c r="C122" t="str">
-        <v>690426-1218</v>
+        <v>690426-9823</v>
       </c>
       <c r="D122" t="str">
         <v>ROM2</v>
@@ -3334,7 +3334,7 @@
         <v>Jakob Persson</v>
       </c>
       <c r="C123" t="str">
-        <v>940822-1738</v>
+        <v>940822-9830</v>
       </c>
       <c r="D123" t="str">
         <v>ROM2</v>
@@ -3363,7 +3363,7 @@
         <v>Kerim Bergström</v>
       </c>
       <c r="C124" t="str">
-        <v>760815-6886</v>
+        <v>760815-9930</v>
       </c>
       <c r="D124" t="str">
         <v>ROM2</v>
@@ -3386,7 +3386,7 @@
         <v>Jonas Olsson</v>
       </c>
       <c r="C125" t="str">
-        <v>691101-7801</v>
+        <v>691101-9955</v>
       </c>
       <c r="D125" t="str">
         <v>KROM</v>
@@ -3415,7 +3415,7 @@
         <v>Wilma Ström</v>
       </c>
       <c r="C126" t="str">
-        <v>801217-6718</v>
+        <v>801217-9936</v>
       </c>
       <c r="D126" t="str">
         <v>KROM</v>
@@ -3444,7 +3444,7 @@
         <v>Agnes Lindqvist</v>
       </c>
       <c r="C127" t="str">
-        <v>910528-7032</v>
+        <v>910528-9947</v>
       </c>
       <c r="D127" t="str">
         <v>KROM</v>
@@ -3467,7 +3467,7 @@
         <v>Nadia Jakobsson</v>
       </c>
       <c r="C128" t="str">
-        <v>040506-1565</v>
+        <v>040506-9832</v>
       </c>
       <c r="D128" t="str">
         <v>Karriärvägledning</v>
@@ -3496,7 +3496,7 @@
         <v>Tilda Nyström</v>
       </c>
       <c r="C129" t="str">
-        <v>630601-4181</v>
+        <v>630601-9883</v>
       </c>
       <c r="D129" t="str">
         <v>ROM2</v>
@@ -3525,7 +3525,7 @@
         <v>Jonas Berg</v>
       </c>
       <c r="C130" t="str">
-        <v>720226-1744</v>
+        <v>720226-9838</v>
       </c>
       <c r="D130" t="str">
         <v>KROM</v>
@@ -3554,7 +3554,7 @@
         <v>Saga Mattsson</v>
       </c>
       <c r="C131" t="str">
-        <v>770116-7996</v>
+        <v>770116-9950</v>
       </c>
       <c r="D131" t="str">
         <v>KROM</v>
@@ -3583,7 +3583,7 @@
         <v>Ahmed Hassan</v>
       </c>
       <c r="C132" t="str">
-        <v>930802-3614</v>
+        <v>930802-9876</v>
       </c>
       <c r="D132" t="str">
         <v>ROM2</v>
@@ -3612,7 +3612,7 @@
         <v>Viktor Bergström</v>
       </c>
       <c r="C133" t="str">
-        <v>740907-1037</v>
+        <v>740907-9824</v>
       </c>
       <c r="D133" t="str">
         <v>KVL</v>
@@ -3635,7 +3635,7 @@
         <v>Arvid Hansson</v>
       </c>
       <c r="C134" t="str">
-        <v>010711-4787</v>
+        <v>010711-9893</v>
       </c>
       <c r="D134" t="str">
         <v>KROM</v>
@@ -3655,7 +3655,7 @@
         <v>Alva Ahmed</v>
       </c>
       <c r="C135" t="str">
-        <v>021220-4572</v>
+        <v>021220-9894</v>
       </c>
       <c r="D135" t="str">
         <v>KROM</v>
@@ -3684,7 +3684,7 @@
         <v>Sofia Olsson</v>
       </c>
       <c r="C136" t="str">
-        <v>790219-7008</v>
+        <v>790219-9939</v>
       </c>
       <c r="D136" t="str">
         <v>Karriärvägledning</v>
@@ -3713,7 +3713,7 @@
         <v>Agnes Yilmaz</v>
       </c>
       <c r="C137" t="str">
-        <v>860919-8836</v>
+        <v>860919-9974</v>
       </c>
       <c r="D137" t="str">
         <v>Karriärvägledning</v>
@@ -3742,7 +3742,7 @@
         <v>Yasmin Karlsson</v>
       </c>
       <c r="C138" t="str">
-        <v>030129-5663</v>
+        <v>030129-9913</v>
       </c>
       <c r="D138" t="str">
         <v>KROM</v>
@@ -3765,7 +3765,7 @@
         <v>Sofia Gustafsson</v>
       </c>
       <c r="C139" t="str">
-        <v>030829-7035</v>
+        <v>030829-9940</v>
       </c>
       <c r="D139" t="str">
         <v>KROM</v>
@@ -3788,7 +3788,7 @@
         <v>Rania Lindberg</v>
       </c>
       <c r="C140" t="str">
-        <v>991217-7384</v>
+        <v>991217-9943</v>
       </c>
       <c r="D140" t="str">
         <v>ROM2</v>
@@ -3811,7 +3811,7 @@
         <v>Anna Ali</v>
       </c>
       <c r="C141" t="str">
-        <v>941209-1739</v>
+        <v>941209-9831</v>
       </c>
       <c r="D141" t="str">
         <v>ROM2</v>
@@ -3840,7 +3840,7 @@
         <v>Klara Jonsson</v>
       </c>
       <c r="C142" t="str">
-        <v>870805-2280</v>
+        <v>870805-9848</v>
       </c>
       <c r="D142" t="str">
         <v>ROM2</v>
@@ -3869,7 +3869,7 @@
         <v>Elias Larsson</v>
       </c>
       <c r="C143" t="str">
-        <v>800521-0169</v>
+        <v>800521-9806</v>
       </c>
       <c r="D143" t="str">
         <v>KROM</v>
@@ -3892,7 +3892,7 @@
         <v>Karl Abdullahi</v>
       </c>
       <c r="C144" t="str">
-        <v>930220-5282</v>
+        <v>930220-9904</v>
       </c>
       <c r="D144" t="str">
         <v>KVL</v>
@@ -3915,7 +3915,7 @@
         <v>Johan Engström</v>
       </c>
       <c r="C145" t="str">
-        <v>811016-0143</v>
+        <v>811016-9805</v>
       </c>
       <c r="D145" t="str">
         <v>KROM</v>
@@ -3938,7 +3938,7 @@
         <v>Ebba Öberg</v>
       </c>
       <c r="C146" t="str">
-        <v>820624-6798</v>
+        <v>820624-9933</v>
       </c>
       <c r="D146" t="str">
         <v>KROM</v>
@@ -3958,7 +3958,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="C147" t="str">
-        <v>960821-4640</v>
+        <v>960821-9896</v>
       </c>
       <c r="D147" t="str">
         <v>KVL</v>
@@ -3981,7 +3981,7 @@
         <v>Johan Karlsson</v>
       </c>
       <c r="C148" t="str">
-        <v>780128-3123</v>
+        <v>780128-9864</v>
       </c>
       <c r="D148" t="str">
         <v>KVL</v>
@@ -4004,7 +4004,7 @@
         <v>Jakob Bengtsson</v>
       </c>
       <c r="C149" t="str">
-        <v>860807-9318</v>
+        <v>860807-9987</v>
       </c>
       <c r="D149" t="str">
         <v>ROM2</v>
@@ -4033,7 +4033,7 @@
         <v>Alva Johansson</v>
       </c>
       <c r="C150" t="str">
-        <v>020516-0708</v>
+        <v>020516-9816</v>
       </c>
       <c r="D150" t="str">
         <v>ROM2</v>
@@ -4056,7 +4056,7 @@
         <v>Leila Gustafsson</v>
       </c>
       <c r="C151" t="str">
-        <v>670525-6870</v>
+        <v>670525-9932</v>
       </c>
       <c r="D151" t="str">
         <v>KROM</v>
@@ -4085,7 +4085,7 @@
         <v>Agnes Holm</v>
       </c>
       <c r="C152" t="str">
-        <v>810604-2180</v>
+        <v>810604-9847</v>
       </c>
       <c r="D152" t="str">
         <v>ROM2</v>
@@ -4105,7 +4105,7 @@
         <v>Emil Hussein</v>
       </c>
       <c r="C153" t="str">
-        <v>050425-5118</v>
+        <v>050425-9904</v>
       </c>
       <c r="D153" t="str">
         <v>ROM2</v>
@@ -4134,7 +4134,7 @@
         <v>Emil Jakobsson</v>
       </c>
       <c r="C154" t="str">
-        <v>840613-2202</v>
+        <v>840613-9843</v>
       </c>
       <c r="D154" t="str">
         <v>KROM</v>
@@ -4163,7 +4163,7 @@
         <v>Sara Karlsson</v>
       </c>
       <c r="C155" t="str">
-        <v>851013-8053</v>
+        <v>851013-9960</v>
       </c>
       <c r="D155" t="str">
         <v>ROM2</v>
@@ -4192,7 +4192,7 @@
         <v>Freja Lundin</v>
       </c>
       <c r="C156" t="str">
-        <v>670122-4831</v>
+        <v>670122-9897</v>
       </c>
       <c r="D156" t="str">
         <v>KVL</v>
@@ -4221,7 +4221,7 @@
         <v>Viktor Åberg</v>
       </c>
       <c r="C157" t="str">
-        <v>010131-0019</v>
+        <v>010131-9804</v>
       </c>
       <c r="D157" t="str">
         <v>ROM2</v>
@@ -4250,7 +4250,7 @@
         <v>Ida Nordin</v>
       </c>
       <c r="C158" t="str">
-        <v>930810-2608</v>
+        <v>930810-9850</v>
       </c>
       <c r="D158" t="str">
         <v>ROM2</v>
@@ -4279,7 +4279,7 @@
         <v>Hugo Lindberg</v>
       </c>
       <c r="C159" t="str">
-        <v>880220-9810</v>
+        <v>880220-9992</v>
       </c>
       <c r="D159" t="str">
         <v>ROM2</v>
@@ -4302,7 +4302,7 @@
         <v>Dalia Jakobsson</v>
       </c>
       <c r="C160" t="str">
-        <v>741204-8261</v>
+        <v>741204-9962</v>
       </c>
       <c r="D160" t="str">
         <v>KVL</v>
@@ -4331,7 +4331,7 @@
         <v>Abdi Berg</v>
       </c>
       <c r="C161" t="str">
-        <v>660808-0385</v>
+        <v>660808-9808</v>
       </c>
       <c r="D161" t="str">
         <v>ROM2</v>
@@ -4351,7 +4351,7 @@
         <v>Gustav Lindström</v>
       </c>
       <c r="C162" t="str">
-        <v>780101-4460</v>
+        <v>780101-9881</v>
       </c>
       <c r="D162" t="str">
         <v>KVL</v>
@@ -4374,7 +4374,7 @@
         <v>Rania Söderberg</v>
       </c>
       <c r="C163" t="str">
-        <v>920622-7267</v>
+        <v>920622-9941</v>
       </c>
       <c r="D163" t="str">
         <v>Karriärvägledning</v>
@@ -4397,7 +4397,7 @@
         <v>Ludvig Engström</v>
       </c>
       <c r="C164" t="str">
-        <v>630201-8558</v>
+        <v>630201-9978</v>
       </c>
       <c r="D164" t="str">
         <v>KROM</v>
@@ -4426,7 +4426,7 @@
         <v>Erik Ali</v>
       </c>
       <c r="C165" t="str">
-        <v>970503-5062</v>
+        <v>970503-9908</v>
       </c>
       <c r="D165" t="str">
         <v>KROM</v>
@@ -4449,7 +4449,7 @@
         <v>Freja Demir</v>
       </c>
       <c r="C166" t="str">
-        <v>020509-2729</v>
+        <v>020509-9856</v>
       </c>
       <c r="D166" t="str">
         <v>KROM</v>
@@ -4478,7 +4478,7 @@
         <v>Jakob Ström</v>
       </c>
       <c r="C167" t="str">
-        <v>010901-3755</v>
+        <v>010901-9877</v>
       </c>
       <c r="D167" t="str">
         <v>KVL</v>
@@ -4501,7 +4501,7 @@
         <v>Alva Bengtsson</v>
       </c>
       <c r="C168" t="str">
-        <v>900107-1480</v>
+        <v>900107-9822</v>
       </c>
       <c r="D168" t="str">
         <v>KROM</v>
@@ -4530,7 +4530,7 @@
         <v>Elias Lindqvist</v>
       </c>
       <c r="C169" t="str">
-        <v>991129-7571</v>
+        <v>991129-9957</v>
       </c>
       <c r="D169" t="str">
         <v>KROM</v>
@@ -4559,7 +4559,7 @@
         <v>Isak Engström</v>
       </c>
       <c r="C170" t="str">
-        <v>630822-6247</v>
+        <v>630822-9928</v>
       </c>
       <c r="D170" t="str">
         <v>ROM2</v>
@@ -4579,7 +4579,7 @@
         <v>Ibrahim Berg</v>
       </c>
       <c r="C171" t="str">
-        <v>710326-0563</v>
+        <v>710326-9812</v>
       </c>
       <c r="D171" t="str">
         <v>ROM2</v>
@@ -4602,7 +4602,7 @@
         <v>Yasmin Forsberg</v>
       </c>
       <c r="C172" t="str">
-        <v>030408-7893</v>
+        <v>030408-9956</v>
       </c>
       <c r="D172" t="str">
         <v>ROM2</v>
@@ -4622,7 +4622,7 @@
         <v>Aisha Karlsson</v>
       </c>
       <c r="C173" t="str">
-        <v>740415-6551</v>
+        <v>740415-9936</v>
       </c>
       <c r="D173" t="str">
         <v>ROM2</v>
@@ -4645,7 +4645,7 @@
         <v>Ida Engström</v>
       </c>
       <c r="C174" t="str">
-        <v>750620-6577</v>
+        <v>750620-9936</v>
       </c>
       <c r="D174" t="str">
         <v>KROM</v>
@@ -4668,7 +4668,7 @@
         <v>Ahmed Pettersson</v>
       </c>
       <c r="C175" t="str">
-        <v>780413-3994</v>
+        <v>780413-9876</v>
       </c>
       <c r="D175" t="str">
         <v>KVL</v>
@@ -4697,7 +4697,7 @@
         <v>Ahmed Fransson</v>
       </c>
       <c r="C176" t="str">
-        <v>920902-5239</v>
+        <v>920902-9900</v>
       </c>
       <c r="D176" t="str">
         <v>KROM</v>
@@ -4720,7 +4720,7 @@
         <v>Hassan Lindqvist</v>
       </c>
       <c r="C177" t="str">
-        <v>810219-0256</v>
+        <v>810219-9802</v>
       </c>
       <c r="D177" t="str">
         <v>KROM</v>
@@ -4743,7 +4743,7 @@
         <v>Dalia Bengtsson</v>
       </c>
       <c r="C178" t="str">
-        <v>990720-5703</v>
+        <v>990720-9911</v>
       </c>
       <c r="D178" t="str">
         <v>ROM2</v>
@@ -4766,7 +4766,7 @@
         <v>Aisha Eriksson</v>
       </c>
       <c r="C179" t="str">
-        <v>940723-8030</v>
+        <v>940723-9962</v>
       </c>
       <c r="D179" t="str">
         <v>ROM2</v>
@@ -4786,7 +4786,7 @@
         <v>Emil Ali</v>
       </c>
       <c r="C180" t="str">
-        <v>670216-7906</v>
+        <v>670216-9951</v>
       </c>
       <c r="D180" t="str">
         <v>ROM2</v>
@@ -4809,7 +4809,7 @@
         <v>Noor Svensson</v>
       </c>
       <c r="C181" t="str">
-        <v>620214-6533</v>
+        <v>620214-9933</v>
       </c>
       <c r="D181" t="str">
         <v>Karriärvägledning</v>
@@ -4832,7 +4832,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="C182" t="str">
-        <v>790403-3565</v>
+        <v>790403-9877</v>
       </c>
       <c r="D182" t="str">
         <v>KVL</v>
@@ -4861,7 +4861,7 @@
         <v>Aisha Eklund</v>
       </c>
       <c r="C183" t="str">
-        <v>671006-3733</v>
+        <v>671006-9870</v>
       </c>
       <c r="D183" t="str">
         <v>KROM</v>
@@ -4881,7 +4881,7 @@
         <v>Rania Abdullahi</v>
       </c>
       <c r="C184" t="str">
-        <v>991105-3115</v>
+        <v>991105-9864</v>
       </c>
       <c r="D184" t="str">
         <v>ROM2</v>
@@ -4904,7 +4904,7 @@
         <v>Axel Forsberg</v>
       </c>
       <c r="C185" t="str">
-        <v>990924-4536</v>
+        <v>990924-9899</v>
       </c>
       <c r="D185" t="str">
         <v>KVL</v>
@@ -4933,7 +4933,7 @@
         <v>Kerim Eklund</v>
       </c>
       <c r="C186" t="str">
-        <v>730525-1329</v>
+        <v>730525-9827</v>
       </c>
       <c r="D186" t="str">
         <v>ROM2</v>
@@ -4962,7 +4962,7 @@
         <v>Vera Nilsson</v>
       </c>
       <c r="C187" t="str">
-        <v>990708-9719</v>
+        <v>990708-9990</v>
       </c>
       <c r="D187" t="str">
         <v>ROM2</v>
@@ -4982,7 +4982,7 @@
         <v>Elias Svensson</v>
       </c>
       <c r="C188" t="str">
-        <v>030821-4998</v>
+        <v>030821-9898</v>
       </c>
       <c r="D188" t="str">
         <v>KVL</v>
@@ -5005,7 +5005,7 @@
         <v>Hassan Larsson</v>
       </c>
       <c r="C189" t="str">
-        <v>750216-1636</v>
+        <v>750216-9837</v>
       </c>
       <c r="D189" t="str">
         <v>ROM2</v>
@@ -5034,7 +5034,7 @@
         <v>Daniel Andersson</v>
       </c>
       <c r="C190" t="str">
-        <v>740511-5747</v>
+        <v>740511-9913</v>
       </c>
       <c r="D190" t="str">
         <v>ROM2</v>
@@ -5057,7 +5057,7 @@
         <v>Hugo Nordin</v>
       </c>
       <c r="C191" t="str">
-        <v>021017-8612</v>
+        <v>021017-9974</v>
       </c>
       <c r="D191" t="str">
         <v>KROM</v>
@@ -5086,7 +5086,7 @@
         <v>Sofia Lundin</v>
       </c>
       <c r="C192" t="str">
-        <v>840107-9721</v>
+        <v>840107-9994</v>
       </c>
       <c r="D192" t="str">
         <v>ROM2</v>
@@ -5115,7 +5115,7 @@
         <v>Selma Eklund</v>
       </c>
       <c r="C193" t="str">
-        <v>951029-0480</v>
+        <v>951029-9804</v>
       </c>
       <c r="D193" t="str">
         <v>ROM2</v>
@@ -5135,7 +5135,7 @@
         <v>Oskar Persson</v>
       </c>
       <c r="C194" t="str">
-        <v>630408-7429</v>
+        <v>630408-9946</v>
       </c>
       <c r="D194" t="str">
         <v>KVL</v>
@@ -5155,7 +5155,7 @@
         <v>Mariam Hassan</v>
       </c>
       <c r="C195" t="str">
-        <v>950724-7493</v>
+        <v>950724-9945</v>
       </c>
       <c r="D195" t="str">
         <v>KROM</v>
@@ -5184,7 +5184,7 @@
         <v>Tilda Axelsson</v>
       </c>
       <c r="C196" t="str">
-        <v>050322-3000</v>
+        <v>050322-9866</v>
       </c>
       <c r="D196" t="str">
         <v>KROM</v>
@@ -5213,7 +5213,7 @@
         <v>Mariam Åberg</v>
       </c>
       <c r="C197" t="str">
-        <v>880225-0657</v>
+        <v>880225-9815</v>
       </c>
       <c r="D197" t="str">
         <v>KROM</v>
@@ -5242,7 +5242,7 @@
         <v>Lucas Mattsson</v>
       </c>
       <c r="C198" t="str">
-        <v>790821-8725</v>
+        <v>790821-9970</v>
       </c>
       <c r="D198" t="str">
         <v>KROM</v>
@@ -5262,7 +5262,7 @@
         <v>Zainab Jansson</v>
       </c>
       <c r="C199" t="str">
-        <v>710228-7419</v>
+        <v>710228-9944</v>
       </c>
       <c r="D199" t="str">
         <v>ROM2</v>
@@ -5291,7 +5291,7 @@
         <v>Lina Hansson</v>
       </c>
       <c r="C200" t="str">
-        <v>681022-5869</v>
+        <v>681022-9911</v>
       </c>
       <c r="D200" t="str">
         <v>KVL</v>
@@ -5320,7 +5320,7 @@
         <v>Karl Eklund</v>
       </c>
       <c r="C201" t="str">
-        <v>851022-2477</v>
+        <v>851022-9845</v>
       </c>
       <c r="D201" t="str">
         <v>ROM2</v>
@@ -5343,7 +5343,7 @@
         <v>Amina Sandberg</v>
       </c>
       <c r="C202" t="str">
-        <v>800930-1519</v>
+        <v>800930-9835</v>
       </c>
       <c r="D202" t="str">
         <v>KROM</v>
@@ -5372,7 +5372,7 @@
         <v>Nadia Eklund</v>
       </c>
       <c r="C203" t="str">
-        <v>670223-5851</v>
+        <v>670223-9911</v>
       </c>
       <c r="D203" t="str">
         <v>Karriärvägledning</v>
@@ -5401,7 +5401,7 @@
         <v>Viktor Eriksson</v>
       </c>
       <c r="C204" t="str">
-        <v>820905-0460</v>
+        <v>820905-9800</v>
       </c>
       <c r="D204" t="str">
         <v>KROM</v>
@@ -5421,7 +5421,7 @@
         <v>Karl Demir</v>
       </c>
       <c r="C205" t="str">
-        <v>710911-8716</v>
+        <v>710911-9979</v>
       </c>
       <c r="D205" t="str">
         <v>ROM2</v>
@@ -5450,7 +5450,7 @@
         <v>Yasmin Fransson</v>
       </c>
       <c r="C206" t="str">
-        <v>840125-8747</v>
+        <v>840125-9976</v>
       </c>
       <c r="D206" t="str">
         <v>ROM2</v>
@@ -5473,7 +5473,7 @@
         <v>Wilma Sjöberg</v>
       </c>
       <c r="C207" t="str">
-        <v>781119-1522</v>
+        <v>781119-9830</v>
       </c>
       <c r="D207" t="str">
         <v>Karriärvägledning</v>
@@ -5502,7 +5502,7 @@
         <v>Anna Ström</v>
       </c>
       <c r="C208" t="str">
-        <v>640115-8487</v>
+        <v>640115-9964</v>
       </c>
       <c r="D208" t="str">
         <v>Karriärvägledning</v>
@@ -5531,7 +5531,7 @@
         <v>Hugo Mattsson</v>
       </c>
       <c r="C209" t="str">
-        <v>780513-8208</v>
+        <v>780513-9966</v>
       </c>
       <c r="D209" t="str">
         <v>Karriärvägledning</v>
@@ -5560,7 +5560,7 @@
         <v>Filip Andersson</v>
       </c>
       <c r="C210" t="str">
-        <v>811027-3292</v>
+        <v>811027-9869</v>
       </c>
       <c r="D210" t="str">
         <v>KROM</v>
@@ -5589,7 +5589,7 @@
         <v>Arvid Lindström</v>
       </c>
       <c r="C211" t="str">
-        <v>030525-8881</v>
+        <v>030525-9970</v>
       </c>
       <c r="D211" t="str">
         <v>Karriärvägledning</v>
@@ -5618,7 +5618,7 @@
         <v>Hanna Lindström</v>
       </c>
       <c r="C212" t="str">
-        <v>950218-2877</v>
+        <v>950218-9856</v>
       </c>
       <c r="D212" t="str">
         <v>Karriärvägledning</v>
@@ -5638,7 +5638,7 @@
         <v>Yasmin Nilsson</v>
       </c>
       <c r="C213" t="str">
-        <v>001030-3394</v>
+        <v>001030-9862</v>
       </c>
       <c r="D213" t="str">
         <v>ROM2</v>
@@ -5667,7 +5667,7 @@
         <v>Aisha Lindström</v>
       </c>
       <c r="C214" t="str">
-        <v>010510-6710</v>
+        <v>010510-9938</v>
       </c>
       <c r="D214" t="str">
         <v>ROM2</v>
@@ -5696,7 +5696,7 @@
         <v>Hassan Ahmed</v>
       </c>
       <c r="C215" t="str">
-        <v>700323-8404</v>
+        <v>700323-9964</v>
       </c>
       <c r="D215" t="str">
         <v>ROM2</v>
@@ -5725,7 +5725,7 @@
         <v>Karl Lundin</v>
       </c>
       <c r="C216" t="str">
-        <v>990319-6336</v>
+        <v>990319-9926</v>
       </c>
       <c r="D216" t="str">
         <v>KROM</v>
@@ -5754,7 +5754,7 @@
         <v>Omar Olsson</v>
       </c>
       <c r="C217" t="str">
-        <v>801004-4363</v>
+        <v>801004-9883</v>
       </c>
       <c r="D217" t="str">
         <v>ROM2</v>
@@ -5774,7 +5774,7 @@
         <v>Anna Svensson</v>
       </c>
       <c r="C218" t="str">
-        <v>800704-0283</v>
+        <v>800704-9805</v>
       </c>
       <c r="D218" t="str">
         <v>KROM</v>
@@ -5797,7 +5797,7 @@
         <v>Saga Sandberg</v>
       </c>
       <c r="C219" t="str">
-        <v>891002-4457</v>
+        <v>891002-9886</v>
       </c>
       <c r="D219" t="str">
         <v>KROM</v>
@@ -5826,7 +5826,7 @@
         <v>Ebba Jansson</v>
       </c>
       <c r="C220" t="str">
-        <v>710131-3679</v>
+        <v>710131-9874</v>
       </c>
       <c r="D220" t="str">
         <v>ROM2</v>
@@ -5846,7 +5846,7 @@
         <v>Ali Jönsson</v>
       </c>
       <c r="C221" t="str">
-        <v>780517-7172</v>
+        <v>780517-9947</v>
       </c>
       <c r="D221" t="str">
         <v>ROM2</v>
@@ -5869,7 +5869,7 @@
         <v>Ebba Hansson</v>
       </c>
       <c r="C222" t="str">
-        <v>970308-4989</v>
+        <v>970308-9897</v>
       </c>
       <c r="D222" t="str">
         <v>Karriärvägledning</v>
@@ -5898,7 +5898,7 @@
         <v>Elias Olsson</v>
       </c>
       <c r="C223" t="str">
-        <v>661215-7922</v>
+        <v>661215-9951</v>
       </c>
       <c r="D223" t="str">
         <v>KROM</v>
@@ -5927,7 +5927,7 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="C224" t="str">
-        <v>910831-6556</v>
+        <v>910831-9931</v>
       </c>
       <c r="D224" t="str">
         <v>ROM2</v>
@@ -5956,7 +5956,7 @@
         <v>Jakob Hansson</v>
       </c>
       <c r="C225" t="str">
-        <v>731213-6299</v>
+        <v>731213-9921</v>
       </c>
       <c r="D225" t="str">
         <v>KROM</v>
@@ -5985,7 +5985,7 @@
         <v>Emil Åberg</v>
       </c>
       <c r="C226" t="str">
-        <v>050818-9834</v>
+        <v>050818-9990</v>
       </c>
       <c r="D226" t="str">
         <v>KROM</v>
@@ -6005,7 +6005,7 @@
         <v>Klara Hussein</v>
       </c>
       <c r="C227" t="str">
-        <v>920207-0877</v>
+        <v>920207-9811</v>
       </c>
       <c r="D227" t="str">
         <v>ROM2</v>
@@ -6025,7 +6025,7 @@
         <v>Axel Ström</v>
       </c>
       <c r="C228" t="str">
-        <v>721209-2667</v>
+        <v>721209-9852</v>
       </c>
       <c r="D228" t="str">
         <v>Karriärvägledning</v>
@@ -6054,7 +6054,7 @@
         <v>Leila Jansson</v>
       </c>
       <c r="C229" t="str">
-        <v>840409-9353</v>
+        <v>840409-9981</v>
       </c>
       <c r="D229" t="str">
         <v>Karriärvägledning</v>
@@ -6077,7 +6077,7 @@
         <v>Freja Jansson</v>
       </c>
       <c r="C230" t="str">
-        <v>670811-5289</v>
+        <v>670811-9901</v>
       </c>
       <c r="D230" t="str">
         <v>ROM2</v>
@@ -6106,7 +6106,7 @@
         <v>Isak Jakobsson</v>
       </c>
       <c r="C231" t="str">
-        <v>010814-0054</v>
+        <v>010814-9808</v>
       </c>
       <c r="D231" t="str">
         <v>KVL</v>
@@ -6129,7 +6129,7 @@
         <v>Ida Olsson</v>
       </c>
       <c r="C232" t="str">
-        <v>621229-8563</v>
+        <v>621229-9975</v>
       </c>
       <c r="D232" t="str">
         <v>KROM</v>
@@ -6152,7 +6152,7 @@
         <v>Oskar Holm</v>
       </c>
       <c r="C233" t="str">
-        <v>620511-2482</v>
+        <v>620511-9842</v>
       </c>
       <c r="D233" t="str">
         <v>KVL</v>
@@ -6181,7 +6181,7 @@
         <v>Vera Eklund</v>
       </c>
       <c r="C234" t="str">
-        <v>670609-8081</v>
+        <v>670609-9964</v>
       </c>
       <c r="D234" t="str">
         <v>KVL</v>
@@ -6210,7 +6210,7 @@
         <v>Selma Persson</v>
       </c>
       <c r="C235" t="str">
-        <v>970207-8479</v>
+        <v>970207-9964</v>
       </c>
       <c r="D235" t="str">
         <v>KROM</v>
@@ -6239,7 +6239,7 @@
         <v>Vera Eriksson</v>
       </c>
       <c r="C236" t="str">
-        <v>990824-3141</v>
+        <v>990824-9866</v>
       </c>
       <c r="D236" t="str">
         <v>KROM</v>
@@ -6268,7 +6268,7 @@
         <v>Abdi Jönsson</v>
       </c>
       <c r="C237" t="str">
-        <v>800525-6527</v>
+        <v>800525-9935</v>
       </c>
       <c r="D237" t="str">
         <v>Karriärvägledning</v>
@@ -6291,7 +6291,7 @@
         <v>Gustav Pettersson</v>
       </c>
       <c r="C238" t="str">
-        <v>800921-9315</v>
+        <v>800921-9984</v>
       </c>
       <c r="D238" t="str">
         <v>ROM2</v>
@@ -6314,7 +6314,7 @@
         <v>Sofia Nyström</v>
       </c>
       <c r="C239" t="str">
-        <v>710815-4142</v>
+        <v>710815-9885</v>
       </c>
       <c r="D239" t="str">
         <v>ROM2</v>
@@ -6337,7 +6337,7 @@
         <v>Samir Axelsson</v>
       </c>
       <c r="C240" t="str">
-        <v>930604-8274</v>
+        <v>930604-9967</v>
       </c>
       <c r="D240" t="str">
         <v>KROM</v>
@@ -6366,7 +6366,7 @@
         <v>Axel Bergström</v>
       </c>
       <c r="C241" t="str">
-        <v>930129-7074</v>
+        <v>930129-9948</v>
       </c>
       <c r="D241" t="str">
         <v>KVL</v>
@@ -6395,7 +6395,7 @@
         <v>Elin Hansson</v>
       </c>
       <c r="C242" t="str">
-        <v>751017-0561</v>
+        <v>751017-9810</v>
       </c>
       <c r="D242" t="str">
         <v>ROM2</v>
@@ -6418,7 +6418,7 @@
         <v>Kerim Ali</v>
       </c>
       <c r="C243" t="str">
-        <v>041119-6520</v>
+        <v>041119-9938</v>
       </c>
       <c r="D243" t="str">
         <v>KROM</v>
@@ -6438,7 +6438,7 @@
         <v>Wilma Åberg</v>
       </c>
       <c r="C244" t="str">
-        <v>730506-1116</v>
+        <v>730506-9820</v>
       </c>
       <c r="D244" t="str">
         <v>KVL</v>
@@ -6467,7 +6467,7 @@
         <v>Saga Mohamed</v>
       </c>
       <c r="C245" t="str">
-        <v>970730-5356</v>
+        <v>970730-9903</v>
       </c>
       <c r="D245" t="str">
         <v>Karriärvägledning</v>
@@ -6490,7 +6490,7 @@
         <v>Hassan Berg</v>
       </c>
       <c r="C246" t="str">
-        <v>760409-3398</v>
+        <v>760409-9866</v>
       </c>
       <c r="D246" t="str">
         <v>ROM2</v>
@@ -6510,7 +6510,7 @@
         <v>Jakob Yilmaz</v>
       </c>
       <c r="C247" t="str">
-        <v>940308-8223</v>
+        <v>940308-9965</v>
       </c>
       <c r="D247" t="str">
         <v>KROM</v>
@@ -6539,7 +6539,7 @@
         <v>Karl Jakobsson</v>
       </c>
       <c r="C248" t="str">
-        <v>000522-4779</v>
+        <v>000522-9893</v>
       </c>
       <c r="D248" t="str">
         <v>ROM2</v>
@@ -6568,7 +6568,7 @@
         <v>Yasmin Berg</v>
       </c>
       <c r="C249" t="str">
-        <v>030613-7720</v>
+        <v>030613-9957</v>
       </c>
       <c r="D249" t="str">
         <v>ROM2</v>
@@ -6591,7 +6591,7 @@
         <v>Ludvig Olsson</v>
       </c>
       <c r="C250" t="str">
-        <v>680301-1144</v>
+        <v>680301-9824</v>
       </c>
       <c r="D250" t="str">
         <v>ROM2</v>
@@ -6611,7 +6611,7 @@
         <v>Zainab Holm</v>
       </c>
       <c r="C251" t="str">
-        <v>811013-0856</v>
+        <v>811013-9816</v>
       </c>
       <c r="D251" t="str">
         <v>KROM</v>
@@ -6640,7 +6640,7 @@
         <v>Ida Svensson</v>
       </c>
       <c r="C252" t="str">
-        <v>940123-7392</v>
+        <v>940123-9943</v>
       </c>
       <c r="D252" t="str">
         <v>KVL</v>
@@ -6669,7 +6669,7 @@
         <v>Alva Axelsson</v>
       </c>
       <c r="C253" t="str">
-        <v>700516-3873</v>
+        <v>700516-9870</v>
       </c>
       <c r="D253" t="str">
         <v>Karriärvägledning</v>
@@ -6692,7 +6692,7 @@
         <v>Wilma Lundin</v>
       </c>
       <c r="C254" t="str">
-        <v>640905-0496</v>
+        <v>640905-9802</v>
       </c>
       <c r="D254" t="str">
         <v>KROM</v>
@@ -6721,7 +6721,7 @@
         <v>Emil Yilmaz</v>
       </c>
       <c r="C255" t="str">
-        <v>870914-6917</v>
+        <v>870914-9937</v>
       </c>
       <c r="D255" t="str">
         <v>ROM2</v>
@@ -6741,7 +6741,7 @@
         <v>Yusuf Ström</v>
       </c>
       <c r="C256" t="str">
-        <v>001130-1249</v>
+        <v>001130-9820</v>
       </c>
       <c r="D256" t="str">
         <v>KROM</v>
@@ -6770,7 +6770,7 @@
         <v>Jonas Jönsson</v>
       </c>
       <c r="C257" t="str">
-        <v>710725-1204</v>
+        <v>710725-9827</v>
       </c>
       <c r="D257" t="str">
         <v>Karriärvägledning</v>
@@ -6799,7 +6799,7 @@
         <v>Emil Demir</v>
       </c>
       <c r="C258" t="str">
-        <v>710124-4395</v>
+        <v>710124-9881</v>
       </c>
       <c r="D258" t="str">
         <v>ROM2</v>
@@ -6819,7 +6819,7 @@
         <v>Maja Wallin</v>
       </c>
       <c r="C259" t="str">
-        <v>031105-1585</v>
+        <v>031105-9836</v>
       </c>
       <c r="D259" t="str">
         <v>KVL</v>
@@ -6848,7 +6848,7 @@
         <v>Zainab Mohamed</v>
       </c>
       <c r="C260" t="str">
-        <v>740412-5663</v>
+        <v>740412-9913</v>
       </c>
       <c r="D260" t="str">
         <v>KROM</v>
@@ -6877,7 +6877,7 @@
         <v>Fatima Nyström</v>
       </c>
       <c r="C261" t="str">
-        <v>850127-2853</v>
+        <v>850127-9858</v>
       </c>
       <c r="D261" t="str">
         <v>KROM</v>
@@ -6906,7 +6906,7 @@
         <v>Aisha Lundin</v>
       </c>
       <c r="C262" t="str">
-        <v>680801-5264</v>
+        <v>680801-9902</v>
       </c>
       <c r="D262" t="str">
         <v>Karriärvägledning</v>
@@ -6929,7 +6929,7 @@
         <v>Elias Karlsson</v>
       </c>
       <c r="C263" t="str">
-        <v>020309-4289</v>
+        <v>020309-9882</v>
       </c>
       <c r="D263" t="str">
         <v>KROM</v>
@@ -6958,7 +6958,7 @@
         <v>Hassan Forsberg</v>
       </c>
       <c r="C264" t="str">
-        <v>800914-3622</v>
+        <v>800914-9876</v>
       </c>
       <c r="D264" t="str">
         <v>Karriärvägledning</v>
@@ -6981,7 +6981,7 @@
         <v>Ida Forsberg</v>
       </c>
       <c r="C265" t="str">
-        <v>851103-4715</v>
+        <v>851103-9896</v>
       </c>
       <c r="D265" t="str">
         <v>ROM2</v>
@@ -7004,7 +7004,7 @@
         <v>Viktor Holm</v>
       </c>
       <c r="C266" t="str">
-        <v>651001-0256</v>
+        <v>651001-9802</v>
       </c>
       <c r="D266" t="str">
         <v>ROM2</v>
@@ -7027,7 +7027,7 @@
         <v>Ebba Eriksson</v>
       </c>
       <c r="C267" t="str">
-        <v>851203-4094</v>
+        <v>851203-9887</v>
       </c>
       <c r="D267" t="str">
         <v>KROM</v>
@@ -7047,7 +7047,7 @@
         <v>Saga Jansson</v>
       </c>
       <c r="C268" t="str">
-        <v>790918-1914</v>
+        <v>790918-9834</v>
       </c>
       <c r="D268" t="str">
         <v>ROM2</v>
@@ -7067,7 +7067,7 @@
         <v>Rania Bengtsson</v>
       </c>
       <c r="C269" t="str">
-        <v>660308-1024</v>
+        <v>660308-9829</v>
       </c>
       <c r="D269" t="str">
         <v>Karriärvägledning</v>
@@ -7090,7 +7090,7 @@
         <v>Daniel Abdullahi</v>
       </c>
       <c r="C270" t="str">
-        <v>931125-2234</v>
+        <v>931125-9841</v>
       </c>
       <c r="D270" t="str">
         <v>ROM2</v>
@@ -7110,7 +7110,7 @@
         <v>Maja Gustafsson</v>
       </c>
       <c r="C271" t="str">
-        <v>761218-0054</v>
+        <v>761218-9808</v>
       </c>
       <c r="D271" t="str">
         <v>Karriärvägledning</v>
@@ -7139,7 +7139,7 @@
         <v>Elin Andersson</v>
       </c>
       <c r="C272" t="str">
-        <v>890619-4397</v>
+        <v>890619-9883</v>
       </c>
       <c r="D272" t="str">
         <v>ROM2</v>
@@ -7159,7 +7159,7 @@
         <v>Viktor Fransson</v>
       </c>
       <c r="C273" t="str">
-        <v>820811-0620</v>
+        <v>820811-9811</v>
       </c>
       <c r="D273" t="str">
         <v>KROM</v>
@@ -7182,7 +7182,7 @@
         <v>Emil Bergström</v>
       </c>
       <c r="C274" t="str">
-        <v>720227-1388</v>
+        <v>720227-9829</v>
       </c>
       <c r="D274" t="str">
         <v>Karriärvägledning</v>
@@ -7208,7 +7208,7 @@
         <v>Johan Berg</v>
       </c>
       <c r="C275" t="str">
-        <v>980407-6991</v>
+        <v>980407-9938</v>
       </c>
       <c r="D275" t="str">
         <v>KROM</v>
@@ -7237,7 +7237,7 @@
         <v>Wilma Wallin</v>
       </c>
       <c r="C276" t="str">
-        <v>720825-3810</v>
+        <v>720825-9874</v>
       </c>
       <c r="D276" t="str">
         <v>Karriärvägledning</v>
@@ -7260,7 +7260,7 @@
         <v>Saga Danielsson</v>
       </c>
       <c r="C277" t="str">
-        <v>840907-4633</v>
+        <v>840907-9897</v>
       </c>
       <c r="D277" t="str">
         <v>ROM2</v>
@@ -7280,7 +7280,7 @@
         <v>Arvid Wallin</v>
       </c>
       <c r="C278" t="str">
-        <v>920308-5890</v>
+        <v>920308-9918</v>
       </c>
       <c r="D278" t="str">
         <v>ROM2</v>
@@ -7309,7 +7309,7 @@
         <v>Saga Gustafsson</v>
       </c>
       <c r="C279" t="str">
-        <v>870705-5631</v>
+        <v>870705-9914</v>
       </c>
       <c r="D279" t="str">
         <v>ROM2</v>
@@ -7329,7 +7329,7 @@
         <v>Emil Pettersson</v>
       </c>
       <c r="C280" t="str">
-        <v>800122-3539</v>
+        <v>800122-9874</v>
       </c>
       <c r="D280" t="str">
         <v>ROM2</v>
@@ -7358,7 +7358,7 @@
         <v>Isak Lindberg</v>
       </c>
       <c r="C281" t="str">
-        <v>030526-4699</v>
+        <v>030526-9896</v>
       </c>
       <c r="D281" t="str">
         <v>Karriärvägledning</v>
@@ -7381,7 +7381,7 @@
         <v>Ibrahim Söderberg</v>
       </c>
       <c r="C282" t="str">
-        <v>810726-0971</v>
+        <v>810726-9816</v>
       </c>
       <c r="D282" t="str">
         <v>Karriärvägledning</v>
@@ -7410,7 +7410,7 @@
         <v>Omar Lindström</v>
       </c>
       <c r="C283" t="str">
-        <v>850517-9971</v>
+        <v>850517-9997</v>
       </c>
       <c r="D283" t="str">
         <v>KROM</v>
@@ -7430,7 +7430,7 @@
         <v>Lucas Nyström</v>
       </c>
       <c r="C284" t="str">
-        <v>700623-2016</v>
+        <v>700623-9847</v>
       </c>
       <c r="D284" t="str">
         <v>KROM</v>
@@ -7450,7 +7450,7 @@
         <v>Hassan Jonsson</v>
       </c>
       <c r="C285" t="str">
-        <v>820415-9837</v>
+        <v>820415-9993</v>
       </c>
       <c r="D285" t="str">
         <v>ROM2</v>
@@ -7479,7 +7479,7 @@
         <v>Yusuf Pettersson</v>
       </c>
       <c r="C286" t="str">
-        <v>910117-8904</v>
+        <v>910117-9977</v>
       </c>
       <c r="D286" t="str">
         <v>ROM2</v>
@@ -7502,7 +7502,7 @@
         <v>Sofia Jonsson</v>
       </c>
       <c r="C287" t="str">
-        <v>031106-2798</v>
+        <v>031106-9850</v>
       </c>
       <c r="D287" t="str">
         <v>KVL</v>
@@ -7525,7 +7525,7 @@
         <v>Isak Nordin</v>
       </c>
       <c r="C288" t="str">
-        <v>651110-5188</v>
+        <v>651110-9909</v>
       </c>
       <c r="D288" t="str">
         <v>Karriärvägledning</v>
@@ -7548,7 +7548,7 @@
         <v>Sara Nyström</v>
       </c>
       <c r="C289" t="str">
-        <v>890804-8674</v>
+        <v>890804-9979</v>
       </c>
       <c r="D289" t="str">
         <v>ROM2</v>
@@ -7571,7 +7571,7 @@
         <v>Alva Berg</v>
       </c>
       <c r="C290" t="str">
-        <v>020316-2110</v>
+        <v>020316-9842</v>
       </c>
       <c r="D290" t="str">
         <v>ROM2</v>
@@ -7600,7 +7600,7 @@
         <v>Samir Nyström</v>
       </c>
       <c r="C291" t="str">
-        <v>960603-8876</v>
+        <v>960603-9973</v>
       </c>
       <c r="D291" t="str">
         <v>ROM2</v>
@@ -7629,7 +7629,7 @@
         <v>Amina Söderberg</v>
       </c>
       <c r="C292" t="str">
-        <v>670514-7509</v>
+        <v>670514-9943</v>
       </c>
       <c r="D292" t="str">
         <v>ROM2</v>
@@ -7649,7 +7649,7 @@
         <v>Anna Berg</v>
       </c>
       <c r="C293" t="str">
-        <v>810430-8203</v>
+        <v>810430-9961</v>
       </c>
       <c r="D293" t="str">
         <v>ROM2</v>
@@ -7678,7 +7678,7 @@
         <v>Aisha Lindqvist</v>
       </c>
       <c r="C294" t="str">
-        <v>700113-7228</v>
+        <v>700113-9943</v>
       </c>
       <c r="D294" t="str">
         <v>KROM</v>
@@ -7707,7 +7707,7 @@
         <v>Sofia Demir</v>
       </c>
       <c r="C295" t="str">
-        <v>811118-5412</v>
+        <v>811118-9901</v>
       </c>
       <c r="D295" t="str">
         <v>ROM2</v>
@@ -7730,7 +7730,7 @@
         <v>Noor Jakobsson</v>
       </c>
       <c r="C296" t="str">
-        <v>880625-8789</v>
+        <v>880625-9977</v>
       </c>
       <c r="D296" t="str">
         <v>KVL</v>
@@ -7759,7 +7759,7 @@
         <v>Hiba Lindberg</v>
       </c>
       <c r="C297" t="str">
-        <v>840915-8774</v>
+        <v>840915-9970</v>
       </c>
       <c r="D297" t="str">
         <v>Karriärvägledning</v>
@@ -7788,7 +7788,7 @@
         <v>Adam Wallin</v>
       </c>
       <c r="C298" t="str">
-        <v>760524-7670</v>
+        <v>760524-9957</v>
       </c>
       <c r="D298" t="str">
         <v>ROM2</v>
@@ -7817,7 +7817,7 @@
         <v>Jonas Danielsson</v>
       </c>
       <c r="C299" t="str">
-        <v>660506-0265</v>
+        <v>660506-9803</v>
       </c>
       <c r="D299" t="str">
         <v>ROM2</v>
@@ -7837,7 +7837,7 @@
         <v>Mohammed Eklund</v>
       </c>
       <c r="C300" t="str">
-        <v>970317-4616</v>
+        <v>970317-9896</v>
       </c>
       <c r="D300" t="str">
         <v>ROM2</v>
@@ -7857,7 +7857,7 @@
         <v>Linnea Wallin</v>
       </c>
       <c r="C301" t="str">
-        <v>700607-2727</v>
+        <v>700607-9854</v>
       </c>
       <c r="D301" t="str">
         <v>Karriärvägledning</v>
@@ -7883,7 +7883,7 @@
         <v>Saga Eriksson</v>
       </c>
       <c r="C302" t="str">
-        <v>001126-7770</v>
+        <v>001126-9958</v>
       </c>
       <c r="D302" t="str">
         <v>Karriärvägledning</v>
@@ -7912,7 +7912,7 @@
         <v>Fatima Jonsson</v>
       </c>
       <c r="C303" t="str">
-        <v>811119-0164</v>
+        <v>811119-9801</v>
       </c>
       <c r="D303" t="str">
         <v>KROM</v>
@@ -7935,7 +7935,7 @@
         <v>Sara Hansson</v>
       </c>
       <c r="C304" t="str">
-        <v>980311-3472</v>
+        <v>980311-9867</v>
       </c>
       <c r="D304" t="str">
         <v>ROM2</v>
